--- a/input/input_exp_He-Xe-T20-P900.xlsx
+++ b/input/input_exp_He-Xe-T20-P900.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/izg5132_psu_edu/Documents/06_PHD_EME_PSU/00 RESEARCH/PHD UHS PROJECT/MATLAB-GITHUB/UHS-CF-Dispersion-Exps2/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="814" documentId="11_F25DC773A252ABDACC1048B8D1997AFC5ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DEC958F-A463-4C05-9140-93C23F79591D}"/>
+  <xr:revisionPtr revIDLastSave="817" documentId="11_F25DC773A252ABDACC1048B8D1997AFC5ADE58F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F80BD837-F98B-47D8-B0F8-1E9DF2D28634}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>path</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>CT_Day4_HP_HQ-12-18-25.dat</t>
+  </si>
+  <si>
+    <t>1A</t>
   </si>
 </sst>
 </file>
@@ -810,13 +813,13 @@
         <v>0.29399999999999998</v>
       </c>
       <c r="S3">
-        <v>30.9</v>
+        <v>35.4</v>
       </c>
       <c r="T3">
-        <v>13.1</v>
+        <v>26.1</v>
       </c>
       <c r="U3">
-        <v>103.8</v>
+        <v>121.3</v>
       </c>
       <c r="V3" t="s">
         <v>46</v>
@@ -827,8 +830,8 @@
       <c r="X3">
         <v>2</v>
       </c>
-      <c r="Y3">
-        <v>1</v>
+      <c r="Y3" t="s">
+        <v>63</v>
       </c>
       <c r="Z3" s="3">
         <v>46008.572916666664</v>
@@ -911,13 +914,13 @@
         <v>0.29399999999999998</v>
       </c>
       <c r="S4">
-        <v>30.9</v>
+        <v>35.4</v>
       </c>
       <c r="T4">
-        <v>13.1</v>
+        <v>26.1</v>
       </c>
       <c r="U4">
-        <v>103.8</v>
+        <v>121.3</v>
       </c>
       <c r="V4" t="s">
         <v>46</v>
@@ -928,8 +931,8 @@
       <c r="X4">
         <v>2</v>
       </c>
-      <c r="Y4">
-        <v>1</v>
+      <c r="Y4" t="s">
+        <v>63</v>
       </c>
       <c r="Z4" s="3">
         <v>46009.529861111114</v>
